--- a/Result/profitability/6114.xlsx
+++ b/Result/profitability/6114.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0.555</v>
+        <v>0.6224999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>14.2825</v>
+        <v>14.305</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.11</v>
       </c>
       <c r="M3" t="n">
-        <v>0.45875</v>
+        <v>0.335</v>
       </c>
       <c r="N3" t="n">
-        <v>10.02625</v>
+        <v>9.345000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>-0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3024999999999999</v>
+        <v>-0.07375000000000007</v>
       </c>
       <c r="N4" t="n">
-        <v>8.673750000000002</v>
+        <v>8.781250000000002</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.43</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2775000000000001</v>
+        <v>0.145</v>
       </c>
       <c r="N5" t="n">
-        <v>6.437500000000001</v>
+        <v>6.015000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08999999999999997</v>
+        <v>-0.1325000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>4.82</v>
+        <v>4.275000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.25</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.31375</v>
+        <v>-0.3700000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4962500000000012</v>
+        <v>0.330000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5125</v>
+        <v>-0.6087500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.004999999999999</v>
+        <v>-3.497499999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-1.3</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.79625</v>
+        <v>-0.7962500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>-7.157499999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-0.83</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.895</v>
+        <v>-0.8950000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>-9.25</v>
@@ -1775,7 +1775,7 @@
         <v>-0.88625</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.941249999999998</v>
+        <v>-7.941249999999999</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>-1.06375</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.423749999999998</v>
+        <v>-9.42375</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>-1.01125</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.47875</v>
+        <v>-8.478749999999998</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>220</v>
+      </c>
+      <c r="D75" t="n">
+        <v>192</v>
+      </c>
+      <c r="E75" t="n">
+        <v>28</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="G75" t="n">
+        <v>11</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>21</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.7675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7938144329896907</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.940000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2383545069570479</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.062893081761006</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.380000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2116468378209142</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
